--- a/output/yearly_total_coral_cover_iteration_32_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_32_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.257782206530967</v>
+        <v>1.259029026115361</v>
       </c>
       <c r="C3" t="n">
-        <v>4.605817212905748</v>
+        <v>4.583963509009213</v>
       </c>
       <c r="D3" t="n">
-        <v>6.070141240554147</v>
+        <v>6.142211339522905</v>
       </c>
       <c r="E3" t="n">
-        <v>11.93374065999086</v>
+        <v>11.98520387464748</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.387640717720756</v>
+        <v>1.401700319992835</v>
       </c>
       <c r="C4" t="n">
-        <v>5.098695806968066</v>
+        <v>4.987535309604341</v>
       </c>
       <c r="D4" t="n">
-        <v>6.279971438092466</v>
+        <v>6.388944392989771</v>
       </c>
       <c r="E4" t="n">
-        <v>12.76630796278129</v>
+        <v>12.77818002258695</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.555823532741835</v>
+        <v>1.595817349492443</v>
       </c>
       <c r="C5" t="n">
-        <v>5.737468793249946</v>
+        <v>5.465651837507604</v>
       </c>
       <c r="D5" t="n">
-        <v>6.528688648414199</v>
+        <v>6.656323056454389</v>
       </c>
       <c r="E5" t="n">
-        <v>13.82198097440598</v>
+        <v>13.71779224345444</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.739196422441378</v>
+        <v>1.823899139062945</v>
       </c>
       <c r="C6" t="n">
-        <v>6.51811524164007</v>
+        <v>6.039548205617495</v>
       </c>
       <c r="D6" t="n">
-        <v>6.802339657252633</v>
+        <v>6.942378352439256</v>
       </c>
       <c r="E6" t="n">
-        <v>15.05965132133408</v>
+        <v>14.8058256971197</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.945208268674663</v>
+        <v>2.087111144929702</v>
       </c>
       <c r="C7" t="n">
-        <v>7.484983508458917</v>
+        <v>6.737498961771493</v>
       </c>
       <c r="D7" t="n">
-        <v>7.118688740163502</v>
+        <v>7.306578825779774</v>
       </c>
       <c r="E7" t="n">
-        <v>16.54888051729708</v>
+        <v>16.13118893248097</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.171282001821948</v>
+        <v>1.314858907212979</v>
       </c>
       <c r="C8" t="n">
-        <v>5.187250989532986</v>
+        <v>4.402226123968466</v>
       </c>
       <c r="D8" t="n">
-        <v>5.447615946070802</v>
+        <v>5.511549493043576</v>
       </c>
       <c r="E8" t="n">
-        <v>11.80614893742574</v>
+        <v>11.22863452422502</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.464661297117114</v>
+        <v>1.673854583854407</v>
       </c>
       <c r="C9" t="n">
-        <v>6.40985223185034</v>
+        <v>5.29725580985367</v>
       </c>
       <c r="D9" t="n">
-        <v>5.922540561139687</v>
+        <v>5.965313802236665</v>
       </c>
       <c r="E9" t="n">
-        <v>13.79705409010714</v>
+        <v>12.93642419594474</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.772667604090679</v>
+        <v>2.060528560643693</v>
       </c>
       <c r="C10" t="n">
-        <v>7.821201066459259</v>
+        <v>6.333128729413716</v>
       </c>
       <c r="D10" t="n">
-        <v>6.457469473986033</v>
+        <v>6.404978136430763</v>
       </c>
       <c r="E10" t="n">
-        <v>16.05133814453597</v>
+        <v>14.79863542648817</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.091902411363502</v>
+        <v>2.468563771891293</v>
       </c>
       <c r="C11" t="n">
-        <v>9.347939183307913</v>
+        <v>7.45159773951317</v>
       </c>
       <c r="D11" t="n">
-        <v>6.945771580986128</v>
+        <v>6.85231128602859</v>
       </c>
       <c r="E11" t="n">
-        <v>18.38561317565754</v>
+        <v>16.77247279743305</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.413486169289264</v>
+        <v>2.893297254736671</v>
       </c>
       <c r="C12" t="n">
-        <v>10.97614425040738</v>
+        <v>8.700510408933512</v>
       </c>
       <c r="D12" t="n">
-        <v>7.475055030781947</v>
+        <v>7.284784420660451</v>
       </c>
       <c r="E12" t="n">
-        <v>20.8646854504786</v>
+        <v>18.87859208433063</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.709518364283183</v>
+        <v>3.333344260174199</v>
       </c>
       <c r="C13" t="n">
-        <v>12.70293929371876</v>
+        <v>10.01333372579339</v>
       </c>
       <c r="D13" t="n">
-        <v>7.958109498099899</v>
+        <v>7.690927134931055</v>
       </c>
       <c r="E13" t="n">
-        <v>23.37056715610184</v>
+        <v>21.03760512089864</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.560291626359456</v>
+        <v>1.941680974505257</v>
       </c>
       <c r="C14" t="n">
-        <v>8.936623549786738</v>
+        <v>7.11565827299567</v>
       </c>
       <c r="D14" t="n">
-        <v>6.089290135590842</v>
+        <v>5.846827905073007</v>
       </c>
       <c r="E14" t="n">
-        <v>16.58620531173704</v>
+        <v>14.90416715257393</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.58353941199602</v>
+        <v>2.039541585664578</v>
       </c>
       <c r="C15" t="n">
-        <v>9.767466814413771</v>
+        <v>7.639283228532749</v>
       </c>
       <c r="D15" t="n">
-        <v>6.103790549182567</v>
+        <v>5.821047210359485</v>
       </c>
       <c r="E15" t="n">
-        <v>17.45479677559236</v>
+        <v>15.49987202455681</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.823851615041555</v>
+        <v>2.424052891509885</v>
       </c>
       <c r="C16" t="n">
-        <v>11.67376560165797</v>
+        <v>9.029604874855954</v>
       </c>
       <c r="D16" t="n">
-        <v>6.553646982222539</v>
+        <v>6.193001963067474</v>
       </c>
       <c r="E16" t="n">
-        <v>20.05126419892207</v>
+        <v>17.64665972943331</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.454645755905456</v>
+        <v>1.978820490156914</v>
       </c>
       <c r="C17" t="n">
-        <v>10.88425391537973</v>
+        <v>8.396495415341272</v>
       </c>
       <c r="D17" t="n">
-        <v>6.07969846052035</v>
+        <v>5.712564089040213</v>
       </c>
       <c r="E17" t="n">
-        <v>18.41859813180554</v>
+        <v>16.0878799945384</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.646282907774434</v>
+        <v>2.31233982024364</v>
       </c>
       <c r="C18" t="n">
-        <v>12.81753112953663</v>
+        <v>9.809593608403002</v>
       </c>
       <c r="D18" t="n">
-        <v>6.476933216612695</v>
+        <v>6.095406423788299</v>
       </c>
       <c r="E18" t="n">
-        <v>20.94074725392376</v>
+        <v>18.21733985243494</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.63831111641595</v>
+        <v>2.369919323097716</v>
       </c>
       <c r="C19" t="n">
-        <v>13.81999371034305</v>
+        <v>10.51583345440703</v>
       </c>
       <c r="D19" t="n">
-        <v>6.55674930496796</v>
+        <v>6.171707855362362</v>
       </c>
       <c r="E19" t="n">
-        <v>22.01505413172696</v>
+        <v>19.05746063286711</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.80601325925539</v>
+        <v>2.696978753290498</v>
       </c>
       <c r="C20" t="n">
-        <v>15.92526330480695</v>
+        <v>12.14080261952226</v>
       </c>
       <c r="D20" t="n">
-        <v>6.939503282422664</v>
+        <v>6.626188320089336</v>
       </c>
       <c r="E20" t="n">
-        <v>24.67077984648501</v>
+        <v>21.4639696929021</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.064607210485241</v>
+        <v>1.635738937430823</v>
       </c>
       <c r="C21" t="n">
-        <v>11.73160035891515</v>
+        <v>8.953568515162038</v>
       </c>
       <c r="D21" t="n">
-        <v>5.779244393112656</v>
+        <v>5.499701551805419</v>
       </c>
       <c r="E21" t="n">
-        <v>18.57545196251305</v>
+        <v>16.08900900439828</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_32_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_32_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.259029026115361</v>
+        <v>1.25616232281896</v>
       </c>
       <c r="C3" t="n">
-        <v>4.583963509009213</v>
+        <v>4.654462811651177</v>
       </c>
       <c r="D3" t="n">
-        <v>6.142211339522905</v>
+        <v>6.124903127497034</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98520387464748</v>
+        <v>12.03552826196717</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.401700319992835</v>
+        <v>1.385011798690325</v>
       </c>
       <c r="C4" t="n">
-        <v>4.987535309604341</v>
+        <v>5.180756993553262</v>
       </c>
       <c r="D4" t="n">
-        <v>6.388944392989771</v>
+        <v>6.435625481290547</v>
       </c>
       <c r="E4" t="n">
-        <v>12.77818002258695</v>
+        <v>13.00139427353413</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.595817349492443</v>
+        <v>1.5539818416356</v>
       </c>
       <c r="C5" t="n">
-        <v>5.465651837507604</v>
+        <v>5.847642654496136</v>
       </c>
       <c r="D5" t="n">
-        <v>6.656323056454389</v>
+        <v>6.816435091108813</v>
       </c>
       <c r="E5" t="n">
-        <v>13.71779224345444</v>
+        <v>14.21805958724055</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.823899139062945</v>
+        <v>1.745832601270944</v>
       </c>
       <c r="C6" t="n">
-        <v>6.039548205617495</v>
+        <v>6.669777878258675</v>
       </c>
       <c r="D6" t="n">
-        <v>6.942378352439256</v>
+        <v>7.132782526398465</v>
       </c>
       <c r="E6" t="n">
-        <v>14.8058256971197</v>
+        <v>15.54839300592808</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.087111144929702</v>
+        <v>1.959657454329415</v>
       </c>
       <c r="C7" t="n">
-        <v>6.737498961771493</v>
+        <v>7.634895975813738</v>
       </c>
       <c r="D7" t="n">
-        <v>7.306578825779774</v>
+        <v>7.617541015829162</v>
       </c>
       <c r="E7" t="n">
-        <v>16.13118893248097</v>
+        <v>17.21209444597232</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.314858907212979</v>
+        <v>1.175933011089742</v>
       </c>
       <c r="C8" t="n">
-        <v>4.402226123968466</v>
+        <v>5.303604839225002</v>
       </c>
       <c r="D8" t="n">
-        <v>5.511549493043576</v>
+        <v>5.876412583349065</v>
       </c>
       <c r="E8" t="n">
-        <v>11.22863452422502</v>
+        <v>12.35595043366381</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.673854583854407</v>
+        <v>1.464428553761143</v>
       </c>
       <c r="C9" t="n">
-        <v>5.29725580985367</v>
+        <v>6.532852681035961</v>
       </c>
       <c r="D9" t="n">
-        <v>5.965313802236665</v>
+        <v>6.404817473299766</v>
       </c>
       <c r="E9" t="n">
-        <v>12.93642419594474</v>
+        <v>14.40209870809687</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.060528560643693</v>
+        <v>1.766841432065687</v>
       </c>
       <c r="C10" t="n">
-        <v>6.333128729413716</v>
+        <v>7.904317226276324</v>
       </c>
       <c r="D10" t="n">
-        <v>6.404978136430763</v>
+        <v>7.018114193404494</v>
       </c>
       <c r="E10" t="n">
-        <v>14.79863542648817</v>
+        <v>16.68927285174651</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.468563771891293</v>
+        <v>2.066492489293914</v>
       </c>
       <c r="C11" t="n">
-        <v>7.45159773951317</v>
+        <v>9.40094512361625</v>
       </c>
       <c r="D11" t="n">
-        <v>6.85231128602859</v>
+        <v>7.600250868959655</v>
       </c>
       <c r="E11" t="n">
-        <v>16.77247279743305</v>
+        <v>19.06768848186982</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.893297254736671</v>
+        <v>2.357181562015803</v>
       </c>
       <c r="C12" t="n">
-        <v>8.700510408933512</v>
+        <v>10.9505125591498</v>
       </c>
       <c r="D12" t="n">
-        <v>7.284784420660451</v>
+        <v>8.203875142294377</v>
       </c>
       <c r="E12" t="n">
-        <v>18.87859208433063</v>
+        <v>21.51156926345998</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.333344260174199</v>
+        <v>2.643431560300205</v>
       </c>
       <c r="C13" t="n">
-        <v>10.01333372579339</v>
+        <v>12.55227277635585</v>
       </c>
       <c r="D13" t="n">
-        <v>7.690927134931055</v>
+        <v>8.703428130465413</v>
       </c>
       <c r="E13" t="n">
-        <v>21.03760512089864</v>
+        <v>23.89913246712147</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.941680974505257</v>
+        <v>1.525449400335737</v>
       </c>
       <c r="C14" t="n">
-        <v>7.11565827299567</v>
+        <v>8.807455004338985</v>
       </c>
       <c r="D14" t="n">
-        <v>5.846827905073007</v>
+        <v>6.598797559140851</v>
       </c>
       <c r="E14" t="n">
-        <v>14.90416715257393</v>
+        <v>16.93170196381557</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.039541585664578</v>
+        <v>1.551073015416578</v>
       </c>
       <c r="C15" t="n">
-        <v>7.639283228532749</v>
+        <v>9.507068053339347</v>
       </c>
       <c r="D15" t="n">
-        <v>5.821047210359485</v>
+        <v>6.651487958427778</v>
       </c>
       <c r="E15" t="n">
-        <v>15.49987202455681</v>
+        <v>17.7096290271837</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.424052891509885</v>
+        <v>1.789971501767997</v>
       </c>
       <c r="C16" t="n">
-        <v>9.029604874855954</v>
+        <v>11.24791289998683</v>
       </c>
       <c r="D16" t="n">
-        <v>6.193001963067474</v>
+        <v>7.231828478839194</v>
       </c>
       <c r="E16" t="n">
-        <v>17.64665972943331</v>
+        <v>20.26971288059402</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.978820490156914</v>
+        <v>1.42979772151097</v>
       </c>
       <c r="C17" t="n">
-        <v>8.396495415341272</v>
+        <v>10.37876183994009</v>
       </c>
       <c r="D17" t="n">
-        <v>5.712564089040213</v>
+        <v>6.756633137552612</v>
       </c>
       <c r="E17" t="n">
-        <v>16.0878799945384</v>
+        <v>18.56519269900367</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.31233982024364</v>
+        <v>1.621798120030518</v>
       </c>
       <c r="C18" t="n">
-        <v>9.809593608403002</v>
+        <v>12.13292900293421</v>
       </c>
       <c r="D18" t="n">
-        <v>6.095406423788299</v>
+        <v>7.209768607924768</v>
       </c>
       <c r="E18" t="n">
-        <v>18.21733985243494</v>
+        <v>20.96449573088949</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.369919323097716</v>
+        <v>1.616889381509285</v>
       </c>
       <c r="C19" t="n">
-        <v>10.51583345440703</v>
+        <v>13.00003802775612</v>
       </c>
       <c r="D19" t="n">
-        <v>6.171707855362362</v>
+        <v>7.328452087891166</v>
       </c>
       <c r="E19" t="n">
-        <v>19.05746063286711</v>
+        <v>21.94537949715657</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.696978753290498</v>
+        <v>1.790570367867588</v>
       </c>
       <c r="C20" t="n">
-        <v>12.14080261952226</v>
+        <v>14.97024859054678</v>
       </c>
       <c r="D20" t="n">
-        <v>6.626188320089336</v>
+        <v>7.774352077683025</v>
       </c>
       <c r="E20" t="n">
-        <v>21.4639696929021</v>
+        <v>24.5351710360974</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.635738937430823</v>
+        <v>1.062624080122663</v>
       </c>
       <c r="C21" t="n">
-        <v>8.953568515162038</v>
+        <v>11.05141609698184</v>
       </c>
       <c r="D21" t="n">
-        <v>5.499701551805419</v>
+        <v>6.502242672428177</v>
       </c>
       <c r="E21" t="n">
-        <v>16.08900900439828</v>
+        <v>18.61628284953267</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_32_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_32_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.25616232281896</v>
+        <v>2.58000303621302</v>
       </c>
       <c r="C3" t="n">
-        <v>4.654462811651177</v>
+        <v>7.7303964023204</v>
       </c>
       <c r="D3" t="n">
-        <v>6.124903127497034</v>
+        <v>8.19012003548897</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03552826196717</v>
+        <v>18.50051947402239</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.385011798690325</v>
+        <v>1.047259577409414</v>
       </c>
       <c r="C4" t="n">
-        <v>5.180756993553262</v>
+        <v>4.546355032781303</v>
       </c>
       <c r="D4" t="n">
-        <v>6.435625481290547</v>
+        <v>5.859178281116312</v>
       </c>
       <c r="E4" t="n">
-        <v>13.00139427353413</v>
+        <v>11.45279289130703</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.5539818416356</v>
+        <v>1.117127505609315</v>
       </c>
       <c r="C5" t="n">
-        <v>5.847642654496136</v>
+        <v>5.249109841940317</v>
       </c>
       <c r="D5" t="n">
-        <v>6.816435091108813</v>
+        <v>6.210447819970222</v>
       </c>
       <c r="E5" t="n">
-        <v>14.21805958724055</v>
+        <v>12.57668516751985</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.745832601270944</v>
+        <v>1.192027330963441</v>
       </c>
       <c r="C6" t="n">
-        <v>6.669777878258675</v>
+        <v>6.160863977933292</v>
       </c>
       <c r="D6" t="n">
-        <v>7.132782526398465</v>
+        <v>6.5978991076488</v>
       </c>
       <c r="E6" t="n">
-        <v>15.54839300592808</v>
+        <v>13.95079041654553</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.959657454329415</v>
+        <v>1.262715122122861</v>
       </c>
       <c r="C7" t="n">
-        <v>7.634895975813738</v>
+        <v>7.22420114407581</v>
       </c>
       <c r="D7" t="n">
-        <v>7.617541015829162</v>
+        <v>7.106751457223698</v>
       </c>
       <c r="E7" t="n">
-        <v>17.21209444597232</v>
+        <v>15.59366772342237</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.175933011089742</v>
+        <v>1.335585612497811</v>
       </c>
       <c r="C8" t="n">
-        <v>5.303604839225002</v>
+        <v>8.419201082720004</v>
       </c>
       <c r="D8" t="n">
-        <v>5.876412583349065</v>
+        <v>7.624813821913002</v>
       </c>
       <c r="E8" t="n">
-        <v>12.35595043366381</v>
+        <v>17.37960051713082</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.464428553761143</v>
+        <v>1.399664874851509</v>
       </c>
       <c r="C9" t="n">
-        <v>6.532852681035961</v>
+        <v>9.750806485086091</v>
       </c>
       <c r="D9" t="n">
-        <v>6.404817473299766</v>
+        <v>8.085779218043951</v>
       </c>
       <c r="E9" t="n">
-        <v>14.40209870809687</v>
+        <v>19.23625057798155</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.766841432065687</v>
+        <v>0.9014505595164637</v>
       </c>
       <c r="C10" t="n">
-        <v>7.904317226276324</v>
+        <v>7.121372044634385</v>
       </c>
       <c r="D10" t="n">
-        <v>7.018114193404494</v>
+        <v>6.386327720987756</v>
       </c>
       <c r="E10" t="n">
-        <v>16.68927285174651</v>
+        <v>14.4091503251386</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.066492489293914</v>
+        <v>0.8081256227507621</v>
       </c>
       <c r="C11" t="n">
-        <v>9.40094512361625</v>
+        <v>7.601377949671779</v>
       </c>
       <c r="D11" t="n">
-        <v>7.600250868959655</v>
+        <v>6.315200099815075</v>
       </c>
       <c r="E11" t="n">
-        <v>19.06768848186982</v>
+        <v>14.72470367223762</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.357181562015803</v>
+        <v>0.8419468311620647</v>
       </c>
       <c r="C12" t="n">
-        <v>10.9505125591498</v>
+        <v>8.998041686164418</v>
       </c>
       <c r="D12" t="n">
-        <v>8.203875142294377</v>
+        <v>6.771172821052506</v>
       </c>
       <c r="E12" t="n">
-        <v>21.51156926345998</v>
+        <v>16.61116133837899</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.643431560300205</v>
+        <v>0.6487977878285471</v>
       </c>
       <c r="C13" t="n">
-        <v>12.55227277635585</v>
+        <v>8.555695623061935</v>
       </c>
       <c r="D13" t="n">
-        <v>8.703428130465413</v>
+        <v>6.234578978342326</v>
       </c>
       <c r="E13" t="n">
-        <v>23.89913246712147</v>
+        <v>15.43907238923281</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.525449400335737</v>
+        <v>0.6788490850555421</v>
       </c>
       <c r="C14" t="n">
-        <v>8.807455004338985</v>
+        <v>10.00936944874019</v>
       </c>
       <c r="D14" t="n">
-        <v>6.598797559140851</v>
+        <v>6.634965144565303</v>
       </c>
       <c r="E14" t="n">
-        <v>16.93170196381557</v>
+        <v>17.32318367836103</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.551073015416578</v>
+        <v>0.6399620584903258</v>
       </c>
       <c r="C15" t="n">
-        <v>9.507068053339347</v>
+        <v>10.80991597921416</v>
       </c>
       <c r="D15" t="n">
-        <v>6.651487958427778</v>
+        <v>6.725001226521778</v>
       </c>
       <c r="E15" t="n">
-        <v>17.7096290271837</v>
+        <v>18.17487926422627</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.789971501767997</v>
+        <v>0.684700301372853</v>
       </c>
       <c r="C16" t="n">
-        <v>11.24791289998683</v>
+        <v>12.68225611336847</v>
       </c>
       <c r="D16" t="n">
-        <v>7.231828478839194</v>
+        <v>7.201011418402888</v>
       </c>
       <c r="E16" t="n">
-        <v>20.26971288059402</v>
+        <v>20.56796783314421</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.42979772151097</v>
+        <v>0.4107141520716532</v>
       </c>
       <c r="C17" t="n">
-        <v>10.37876183994009</v>
+        <v>9.578725818272321</v>
       </c>
       <c r="D17" t="n">
-        <v>6.756633137552612</v>
+        <v>6.014873659608933</v>
       </c>
       <c r="E17" t="n">
-        <v>18.56519269900367</v>
+        <v>16.00431362995291</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.621798120030518</v>
+        <v>0.3043516057935537</v>
       </c>
       <c r="C18" t="n">
-        <v>12.13292900293421</v>
+        <v>8.68345045181557</v>
       </c>
       <c r="D18" t="n">
-        <v>7.209768607924768</v>
+        <v>5.523616925880872</v>
       </c>
       <c r="E18" t="n">
-        <v>20.96449573088949</v>
+        <v>14.51141898349</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.616889381509285</v>
+        <v>0.3463115026730624</v>
       </c>
       <c r="C19" t="n">
-        <v>13.00003802775612</v>
+        <v>10.81754415887616</v>
       </c>
       <c r="D19" t="n">
-        <v>7.328452087891166</v>
+        <v>6.079266491530482</v>
       </c>
       <c r="E19" t="n">
-        <v>21.94537949715657</v>
+        <v>17.2431221530797</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.790570367867588</v>
+        <v>0.3859348400164637</v>
       </c>
       <c r="C20" t="n">
-        <v>14.97024859054678</v>
+        <v>13.13325137374536</v>
       </c>
       <c r="D20" t="n">
-        <v>7.774352077683025</v>
+        <v>6.707015608579977</v>
       </c>
       <c r="E20" t="n">
-        <v>24.5351710360974</v>
+        <v>20.22620182234181</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.062624080122663</v>
+        <v>0.4228485536961437</v>
       </c>
       <c r="C21" t="n">
-        <v>11.05141609698184</v>
+        <v>15.42315825894697</v>
       </c>
       <c r="D21" t="n">
-        <v>6.502242672428177</v>
+        <v>7.296996891447097</v>
       </c>
       <c r="E21" t="n">
-        <v>18.61628284953267</v>
+        <v>23.14300370409021</v>
       </c>
     </row>
   </sheetData>
